--- a/Freight_Loader_Import_Template.xlsx
+++ b/Freight_Loader_Import_Template.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K6"/>
+  <dimension ref="A1:L6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -503,6 +503,7 @@
     <col width="16" customWidth="1" min="9" max="9"/>
     <col width="30" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="9" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -559,6 +560,11 @@
       <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Stackable?</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Stop #</t>
         </is>
       </c>
     </row>
@@ -586,6 +592,11 @@
       </c>
       <c r="J2" s="3" t="n"/>
       <c r="K2" s="3" t="n"/>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>stop ID 1–10</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="18" customHeight="1">
       <c r="A3" s="4" t="n">
@@ -631,6 +642,9 @@
           <t>Y</t>
         </is>
       </c>
+      <c r="L3" s="4" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="4" ht="18" customHeight="1">
       <c r="A4" s="6" t="n">
@@ -676,6 +690,9 @@
           <t>N</t>
         </is>
       </c>
+      <c r="L4" s="6" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="4" t="n">
@@ -717,6 +734,9 @@
           <t>Y</t>
         </is>
       </c>
+      <c r="L5" s="4" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="6" ht="18" customHeight="1">
       <c r="A6" s="6" t="n">
@@ -761,6 +781,9 @@
         <is>
           <t>Y</t>
         </is>
+      </c>
+      <c r="L6" s="6" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
